--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487172_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487172_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2644</v>
+        <v>4.7294</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2142</v>
+        <v>3.3692</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0502</v>
+        <v>1.3602</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0173</v>
+        <v>5.0001</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.5329</v>
+        <v>-0.4636</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5501</v>
+        <v>5.4637</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8266</v>
+        <v>6.6427</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9312</v>
+        <v>2.1009</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8954</v>
+        <v>4.5419</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8094</v>
+        <v>-1.6426</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.4641</v>
+        <v>-2.5644</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.9218</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3511</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.193</v>
+        <v>-4.0532</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5441</v>
+        <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>2.954</v>
+        <v>1.1805</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0089</v>
+        <v>0.4938</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0549</v>
+        <v>0.6867</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9421</v>
+        <v>0.2859</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5717</v>
+        <v>0.2859</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8325</v>
+        <v>3.675</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9905</v>
+        <v>3.3304</v>
       </c>
       <c r="F3" t="n">
-        <v>1.842</v>
+        <v>0.3446</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0001</v>
+        <v>0.0173</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4636</v>
+        <v>-1.5329</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4637</v>
+        <v>1.5501</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6427</v>
+        <v>1.8266</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1009</v>
+        <v>0.9312</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5419</v>
+        <v>0.8954</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6426</v>
+        <v>-1.8094</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.5644</v>
+        <v>-2.4641</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9218</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0532</v>
+        <v>-0.193</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3161</v>
+        <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2836</v>
+        <v>1.3646</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1151</v>
+        <v>1.125</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1686</v>
+        <v>0.2396</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2859</v>
+        <v>0.9421</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>0.5717</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3864</v>
+        <v>2.5262</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8985</v>
+        <v>1.958</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4879</v>
+        <v>0.5682</v>
       </c>
       <c r="G4" t="n">
         <v>1.3721</v>
@@ -766,13 +766,13 @@
         <v>1.3511</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1421</v>
+        <v>0.2819</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1917</v>
+        <v>0.2512</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0496</v>
+        <v>0.0307</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2859</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8033</v>
+        <v>1.728</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0596</v>
+        <v>1.2787</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7437</v>
+        <v>0.4493</v>
       </c>
       <c r="G5" t="n">
         <v>-2.6484</v>
@@ -844,13 +844,13 @@
         <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1997</v>
+        <v>1.1243</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2935</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9062</v>
+        <v>0.6117</v>
       </c>
       <c r="V5" t="n">
         <v>5.5681</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8182</v>
+        <v>1.4191</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2108</v>
+        <v>-0.8509</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0291</v>
+        <v>2.27</v>
       </c>
       <c r="G6" t="n">
         <v>0.5691000000000001</v>
@@ -922,13 +922,13 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5228</v>
+        <v>0.078</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3424</v>
+        <v>0.0175</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1805</v>
+        <v>0.0605</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5213</v>
+        <v>0.0786</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9386</v>
+        <v>-0.1781</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4173</v>
+        <v>0.2567</v>
       </c>
       <c r="G7" t="n">
         <v>0.7019</v>
@@ -1000,13 +1000,13 @@
         <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1653</v>
+        <v>0.4346</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8328</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6676</v>
+        <v>0.507</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6564</v>
+        <v>-2.4248</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0759</v>
+        <v>-0.8176</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5805</v>
+        <v>-1.6073</v>
       </c>
       <c r="G8" t="n">
         <v>0.09180000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0358</v>
+        <v>0.2674</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9333</v>
+        <v>0.1917</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1024</v>
+        <v>0.0757</v>
       </c>
       <c r="V8" t="n">
         <v>-2.784</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8679</v>
+        <v>-2.4277</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5103</v>
+        <v>-1.1504</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3576</v>
+        <v>-1.2773</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4326</v>
@@ -1156,13 +1156,13 @@
         <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5704</v>
+        <v>-0.1302</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5208</v>
+        <v>-0.1609</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0496</v>
+        <v>0.0307</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2859</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2918</v>
+        <v>-2.5521</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7386</v>
+        <v>-1.9186</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5532</v>
+        <v>-0.6335</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7443</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3351</v>
+        <v>0.4045</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6253</v>
+        <v>0.1947</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2901</v>
+        <v>0.2098</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5983</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0343</v>
+        <v>-3.1261</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5449</v>
+        <v>-1.9847</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4893</v>
+        <v>-1.1413</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2999</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3483</v>
+        <v>0.5599</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1652</v>
+        <v>0.395</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1831</v>
+        <v>0.1649</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7331</v>
+        <v>3.625599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.143699999999999</v>
+        <v>3.036</v>
       </c>
       <c r="F12" t="n">
         <v>0.5896000000000003</v>
@@ -1390,13 +1390,13 @@
         <v>13.5107</v>
       </c>
       <c r="S12" t="n">
-        <v>4.673300000000001</v>
+        <v>5.5655</v>
       </c>
       <c r="T12" t="n">
-        <v>2.056</v>
+        <v>2.9482</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6172</v>
+        <v>2.6173</v>
       </c>
       <c r="V12" t="n">
         <v>0.3281000000000007</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.282</v>
+        <v>7.0365</v>
       </c>
       <c r="E13" t="n">
-        <v>7.5049</v>
+        <v>8.2059</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2229</v>
+        <v>-1.1693</v>
       </c>
       <c r="G13" t="n">
         <v>4.2069</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5666</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2492</v>
+        <v>-0.5483</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3173</v>
+        <v>-0.2638</v>
       </c>
       <c r="V13" t="n">
         <v>3.6417</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9153</v>
+        <v>3.8148</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5837</v>
+        <v>3.4836</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3316</v>
+        <v>0.3313</v>
       </c>
       <c r="G14" t="n">
         <v>2.2152</v>
@@ -1546,13 +1546,13 @@
         <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3563</v>
+        <v>0.2558</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1917</v>
+        <v>0.0916</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1646</v>
+        <v>0.1642</v>
       </c>
       <c r="V14" t="n">
         <v>0.5717</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9022</v>
+        <v>2.7039</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1231</v>
+        <v>2.5236</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2209</v>
+        <v>0.1803</v>
       </c>
       <c r="G15" t="n">
         <v>3.769</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0332</v>
+        <v>-1.2314</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1898</v>
+        <v>-0.7892</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8435</v>
+        <v>-0.4422</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4126</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5482</v>
+        <v>0.9689</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3308</v>
+        <v>-2.2307</v>
       </c>
       <c r="F16" t="n">
-        <v>2.879</v>
+        <v>3.1996</v>
       </c>
       <c r="G16" t="n">
         <v>-2.463</v>
@@ -1702,13 +1702,13 @@
         <v>2.8951</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1964</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6411</v>
+        <v>-0.541</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5553</v>
+        <v>-0.2347</v>
       </c>
       <c r="V16" t="n">
         <v>1.3125</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4345</v>
+        <v>-0.3813</v>
       </c>
       <c r="E17" t="n">
         <v>-0.784</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3495</v>
+        <v>0.4027</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3519</v>
@@ -1780,13 +1780,13 @@
         <v>0.193</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2756</v>
+        <v>-0.2224</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.044</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6282</v>
+        <v>-0.6014</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0181</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6101</v>
+        <v>-0.5834</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5125</v>
@@ -1858,13 +1858,13 @@
         <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3087</v>
+        <v>-0.2819</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2492</v>
+        <v>-0.2224</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.9103</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5912</v>
+        <v>-1.8917</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7943</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7078</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3318</v>
+        <v>0.2185</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3702</v>
+        <v>0.0697</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0383</v>
+        <v>0.1487</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. JUSTO ANTOLIN</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.269</v>
+        <v>-1.1392</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2164</v>
+        <v>-0.2998</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0526</v>
+        <v>-0.8394</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3631</v>
+        <v>-0.0062</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7711</v>
+        <v>0.1895</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1342</v>
+        <v>-0.1956</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2113</v>
+        <v>1.0219</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5058</v>
+        <v>1.0711</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2945</v>
+        <v>-0.0492</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5744</v>
+        <v>-1.028</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7347</v>
+        <v>-0.8817</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8397</v>
+        <v>-0.1464</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.193</v>
+        <v>0.193</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0833</v>
+        <v>0.5159</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5024</v>
+        <v>-0.0056</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5857</v>
+        <v>0.5215</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3704</v>
+        <v>-1.842</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3704</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>A. JUSTO ANTOLIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3193</v>
+        <v>-1.6828</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4</v>
+        <v>-1.8172</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9194</v>
+        <v>0.1344</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0062</v>
+        <v>-1.3631</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1895</v>
+        <v>0.7711</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1956</v>
+        <v>-2.1342</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0219</v>
+        <v>0.2113</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0711</v>
+        <v>1.5058</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0492</v>
+        <v>-1.2945</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.028</v>
+        <v>-1.5744</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8817</v>
+        <v>-0.7347</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1464</v>
+        <v>-0.8397</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1231</v>
+        <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3358</v>
+        <v>-0.4971</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1057</v>
+        <v>-0.0985</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4415</v>
+        <v>-0.3986</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.842</v>
+        <v>0.3704</v>
       </c>
       <c r="W21" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4559</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9513</v>
+        <v>-2.5789</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2392</v>
+        <v>-2.8401</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2879</v>
+        <v>0.2612</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3194</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1752</v>
+        <v>-0.4525</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4429</v>
+        <v>-0.158</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2677</v>
+        <v>-0.2945</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.871</v>
+        <v>-3.0713</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1105</v>
+        <v>0.9102</v>
       </c>
       <c r="F23" t="n">
         <v>-3.9815</v>
@@ -2248,10 +2248,10 @@
         <v>0.193</v>
       </c>
       <c r="S23" t="n">
-        <v>0.193</v>
+        <v>-0.0073</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1322</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U23" t="n">
         <v>0.0608</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1106</v>
+        <v>-5.557</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.332</v>
+        <v>-5.8313</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2214</v>
+        <v>0.2743</v>
       </c>
       <c r="G24" t="n">
         <v>-2.544</v>
@@ -2326,13 +2326,13 @@
         <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6015</v>
+        <v>-0.0479</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8328</v>
+        <v>-0.3321</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2313</v>
+        <v>0.2842</v>
       </c>
       <c r="V24" t="n">
         <v>-1.228</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7331</v>
+        <v>-1.398099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.5895000000000001</v>
+        <v>-0.5896000000000017</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1437</v>
+        <v>-0.8084</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6269999999999996</v>
+        <v>-0.6269999999999991</v>
       </c>
       <c r="H25" t="n">
         <v>8.212700000000002</v>
@@ -2377,22 +2377,22 @@
         <v>-8.839600000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>6.910300000000002</v>
+        <v>6.910299999999999</v>
       </c>
       <c r="K25" t="n">
         <v>12.1546</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.244199999999999</v>
+        <v>-5.2442</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.537200000000001</v>
+        <v>-7.5372</v>
       </c>
       <c r="N25" t="n">
         <v>-3.9419</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.5953</v>
+        <v>-3.595300000000001</v>
       </c>
       <c r="P25" t="n">
         <v>2.895</v>
@@ -2404,13 +2404,13 @@
         <v>16.4056</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.6732</v>
+        <v>-3.338</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.6172</v>
+        <v>-2.6175</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.056</v>
+        <v>-0.7208000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3281000000000003</v>
